--- a/output/pdf_financials_xlsx/AMG.P.xlsx
+++ b/output/pdf_financials_xlsx/AMG.P.xlsx
@@ -1418,19 +1418,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.327372</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.462221</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.424628</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.391805</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.371904</v>
       </c>
     </row>
     <row r="35">
@@ -1462,19 +1462,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.327372</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.462221</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.424628</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.391805</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.371904</v>
       </c>
     </row>
     <row r="37">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">

--- a/output/pdf_financials_xlsx/AMG.P.xlsx
+++ b/output/pdf_financials_xlsx/AMG.P.xlsx
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.145001</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.171117</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -6412,7 +6412,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.145001</v>
       </c>
